--- a/tests/test-data/TC1_remedial_actions.xlsx
+++ b/tests/test-data/TC1_remedial_actions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\martynas.karobcikas\Documents\python_projects\nc-data-exchange\tests\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3717EE8E-7B6B-4756-95D0-3D0B0D24670B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53CAFD09-4CD3-4431-B45C-49C723891E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{D1B4CF46-DF8C-4359-90CF-6EF21FC24236}"/>
   </bookViews>
